--- a/survey_templates/040_sustainable_gift_ideas_survey--survey_templates.xlsx
+++ b/survey_templates/040_sustainable_gift_ideas_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,8 +949,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,12 +978,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'eco_friendly',_'label':_'eco-friendly'}</t>
+          <t>eco-friendly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'eco_friendly', 'label': 'Eco-friendly'}</t>
+          <t>Eco-friendly</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sustainable',_'label':_'sustainable'}</t>
+          <t>sustainable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'sustainable', 'label': 'Sustainable'}</t>
+          <t>Sustainable</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_important',_'label':_'not_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_important', 'label': 'Not important'}</t>
+          <t>Not important</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'experience',_'label':_'experience'}</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'experience', 'label': 'Experience'}</t>
+          <t>Experience</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'physical',_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'physical', 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'digital',_'label':_'digital'}</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'digital', 'label': 'Digital'}</t>
+          <t>Digital</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'eco_friendly_repeat',_'label':_'eco-friendly',_'hint':_none,_'required':_true}</t>
+          <t>eco-friendly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'eco_friendly_repeat', 'label': 'Eco-friendly', 'hint': None, 'required': True}</t>
+          <t>Eco-friendly</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sustainable_repeat',_'label':_'sustainable',_'hint':_none}</t>
+          <t>sustainable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'sustainable_repeat', 'label': 'Sustainable', 'hint': None}</t>
+          <t>Sustainable</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_important_repeat',_'label':_'not_important',_'hint':_none}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_important_repeat', 'label': 'Not important', 'hint': None}</t>
+          <t>Not important</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'experience_repeat',_'label':_'experience',_'hint':_none}</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'experience_repeat', 'label': 'Experience', 'hint': None}</t>
+          <t>Experience</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'physical_repeat',_'label':_'physical',_'hint':_none}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'physical_repeat', 'label': 'Physical', 'hint': None}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'digital_repeat',_'label':_'digital',_'hint':_none}</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'digital_repeat', 'label': 'Digital', 'hint': None}</t>
+          <t>Digital</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other_repeat',_'label':_'other',_'hint':_none}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other_repeat', 'label': 'Other', 'hint': None}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
